--- a/output/stock_quant_scores/C_income_df.xlsx
+++ b/output/stock_quant_scores/C_income_df.xlsx
@@ -1200,13 +1200,17 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>10.797836</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>21952000000</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1227,7 +1231,9 @@
       </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>71887000000</v>
+      </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
